--- a/agility-wiki/backend/data/agility_employee.xlsx
+++ b/agility-wiki/backend/data/agility_employee.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="858">
   <si>
     <t>name</t>
   </si>
@@ -131,6 +131,9 @@
     <t>anhtran@asnet.com.vn</t>
   </si>
   <si>
+    <t>HR</t>
+  </si>
+  <si>
     <t>AT</t>
   </si>
   <si>
@@ -593,328 +596,331 @@
     <t>binh.huynh@asnet.com.vn</t>
   </si>
   <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>Võ Phước</t>
+  </si>
+  <si>
+    <t>(096) 703-4341</t>
+  </si>
+  <si>
+    <t>phuoc.vo@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thanh Hà</t>
+  </si>
+  <si>
+    <t>(093) 542-5803</t>
+  </si>
+  <si>
+    <t>ha.nguyenthanh@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Huỳnh Thị Hà Ngân</t>
+  </si>
+  <si>
+    <t>(093) 527-8159</t>
+  </si>
+  <si>
+    <t>ngan.huynh@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Ngô Hoàng Thế Duy</t>
+  </si>
+  <si>
+    <t>(090) 561-9671</t>
+  </si>
+  <si>
+    <t>duy.ngo@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Hà Y Thảo</t>
+  </si>
+  <si>
+    <t>(094) 768-0523</t>
+  </si>
+  <si>
+    <t>thao.ha@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Trường Giang</t>
+  </si>
+  <si>
+    <t>(088) 622-7471</t>
+  </si>
+  <si>
+    <t>giang.nguyen@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Phạm Xuân Việt</t>
+  </si>
+  <si>
+    <t>(079) 461-6145</t>
+  </si>
+  <si>
+    <t>viet.pham@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>huy.nguyenduc@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Hồ Quang Thắng</t>
+  </si>
+  <si>
+    <t>(097) 150-4302</t>
+  </si>
+  <si>
+    <t>thang.hoquang@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Dương Thế Hiển</t>
+  </si>
+  <si>
+    <t>(076) 840-9337</t>
+  </si>
+  <si>
+    <t>hien.duong@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Hóa</t>
+  </si>
+  <si>
+    <t>(091) 959-1905</t>
+  </si>
+  <si>
+    <t>hoa.nguyen@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Phan Hữu Lợi</t>
+  </si>
+  <si>
+    <t>(032) 776-8351</t>
+  </si>
+  <si>
+    <t>loi.phan@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Ngô Thị Ni</t>
+  </si>
+  <si>
+    <t>(077) 353-5348</t>
+  </si>
+  <si>
+    <t>ni.ngo@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Tấn Bảo</t>
+  </si>
+  <si>
+    <t>(098) 754-5462</t>
+  </si>
+  <si>
+    <t>bao.nguyen@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>5A</t>
+  </si>
+  <si>
+    <t>Dương Công Nhật</t>
+  </si>
+  <si>
+    <t>(086) 825-2304</t>
+  </si>
+  <si>
+    <t>nhat.duong@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Đoàn Ngọc Nhân</t>
+  </si>
+  <si>
+    <t>(037) 462-9235</t>
+  </si>
+  <si>
+    <t>nhan.doanngoc@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>5B</t>
+  </si>
+  <si>
+    <t>Phạm Khắc Trước</t>
+  </si>
+  <si>
+    <t>(090) 631-4267</t>
+  </si>
+  <si>
+    <t>truoc.phamkhac@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Lê Xuân Phương</t>
+  </si>
+  <si>
+    <t>(079) 452-2199</t>
+  </si>
+  <si>
+    <t>phuong.lexuan@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Phạm Nguyên Đức</t>
+  </si>
+  <si>
+    <t>(077) 743-7069</t>
+  </si>
+  <si>
+    <t>duc.pham@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Huy</t>
+  </si>
+  <si>
+    <t>(078) 757-5997</t>
+  </si>
+  <si>
+    <t>huy.nguyenvan@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Trần Thị Nhàn</t>
+  </si>
+  <si>
+    <t>(096) 649-5870</t>
+  </si>
+  <si>
+    <t>nhan.tran@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Mai Đăng Tùng</t>
+  </si>
+  <si>
+    <t>(070) 405-8094</t>
+  </si>
+  <si>
+    <t>tung.mai@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Ngô Thị Trung Hiếu</t>
+  </si>
+  <si>
+    <t>(097) 811-3915</t>
+  </si>
+  <si>
+    <t>hieu.ngo@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Tôn Nữ Minh Trang</t>
+  </si>
+  <si>
+    <t>(093) 596-9600</t>
+  </si>
+  <si>
+    <t>trang.ton@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Huỳnh Ngọc Minh</t>
+  </si>
+  <si>
+    <t>(090) 593-7472</t>
+  </si>
+  <si>
+    <t>minh.huynh@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Phạm Văn Phú Thịnh</t>
+  </si>
+  <si>
+    <t>(090) 590-1869</t>
+  </si>
+  <si>
+    <t>thinh.pham@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Hồ Khắc Hoàng</t>
+  </si>
+  <si>
+    <t>(097) 345-1505</t>
+  </si>
+  <si>
+    <t>hoang.ho@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Trương Thị Vĩ Ngọc</t>
+  </si>
+  <si>
+    <t>(093) 494-4470</t>
+  </si>
+  <si>
+    <t>ngoc.truong@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>BA QA</t>
+  </si>
+  <si>
+    <t>Trần Trọng Tuyển</t>
+  </si>
+  <si>
+    <t>(094) 643-9269</t>
+  </si>
+  <si>
+    <t>tuyen.trantrong@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Hồ Kim Lân</t>
+  </si>
+  <si>
+    <t>(078) 247-6853</t>
+  </si>
+  <si>
+    <t>lan.ho@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Dương Quang Sang</t>
+  </si>
+  <si>
+    <t>(093) 535-3972</t>
+  </si>
+  <si>
+    <t>sang.duong@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Trần Thị Tuyết</t>
+  </si>
+  <si>
+    <t>(094) 422-6877</t>
+  </si>
+  <si>
+    <t>tuyet.tran@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Thành</t>
+  </si>
+  <si>
+    <t>(090) 657-1099</t>
+  </si>
+  <si>
+    <t>thanh.nguyencong@asnet.com.vn</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>HPT</t>
+  </si>
+  <si>
+    <t>Trần Công Thành</t>
+  </si>
+  <si>
+    <t>(090) 886-4282</t>
+  </si>
+  <si>
+    <t>thanh.trancong@asnet.com.vn</t>
+  </si>
+  <si>
     <t>DevOps Engineer</t>
   </si>
   <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>Võ Phước</t>
-  </si>
-  <si>
-    <t>(096) 703-4341</t>
-  </si>
-  <si>
-    <t>phuoc.vo@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thanh Hà</t>
-  </si>
-  <si>
-    <t>(093) 542-5803</t>
-  </si>
-  <si>
-    <t>ha.nguyenthanh@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Huỳnh Thị Hà Ngân</t>
-  </si>
-  <si>
-    <t>(093) 527-8159</t>
-  </si>
-  <si>
-    <t>ngan.huynh@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Ngô Hoàng Thế Duy</t>
-  </si>
-  <si>
-    <t>(090) 561-9671</t>
-  </si>
-  <si>
-    <t>duy.ngo@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Hà Y Thảo</t>
-  </si>
-  <si>
-    <t>(094) 768-0523</t>
-  </si>
-  <si>
-    <t>thao.ha@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Nguyễn Trường Giang</t>
-  </si>
-  <si>
-    <t>(088) 622-7471</t>
-  </si>
-  <si>
-    <t>giang.nguyen@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Phạm Xuân Việt</t>
-  </si>
-  <si>
-    <t>(079) 461-6145</t>
-  </si>
-  <si>
-    <t>viet.pham@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>huy.nguyenduc@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Hồ Quang Thắng</t>
-  </si>
-  <si>
-    <t>(097) 150-4302</t>
-  </si>
-  <si>
-    <t>thang.hoquang@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Dương Thế Hiển</t>
-  </si>
-  <si>
-    <t>(076) 840-9337</t>
-  </si>
-  <si>
-    <t>hien.duong@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Hóa</t>
-  </si>
-  <si>
-    <t>(091) 959-1905</t>
-  </si>
-  <si>
-    <t>hoa.nguyen@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Phan Hữu Lợi</t>
-  </si>
-  <si>
-    <t>(032) 776-8351</t>
-  </si>
-  <si>
-    <t>loi.phan@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Ngô Thị Ni</t>
-  </si>
-  <si>
-    <t>(077) 353-5348</t>
-  </si>
-  <si>
-    <t>ni.ngo@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Nguyễn Tấn Bảo</t>
-  </si>
-  <si>
-    <t>(098) 754-5462</t>
-  </si>
-  <si>
-    <t>bao.nguyen@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>5A</t>
-  </si>
-  <si>
-    <t>Dương Công Nhật</t>
-  </si>
-  <si>
-    <t>(086) 825-2304</t>
-  </si>
-  <si>
-    <t>nhat.duong@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Đoàn Ngọc Nhân</t>
-  </si>
-  <si>
-    <t>(037) 462-9235</t>
-  </si>
-  <si>
-    <t>nhan.doanngoc@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>5B</t>
-  </si>
-  <si>
-    <t>Phạm Khắc Trước</t>
-  </si>
-  <si>
-    <t>(090) 631-4267</t>
-  </si>
-  <si>
-    <t>truoc.phamkhac@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Lê Xuân Phương</t>
-  </si>
-  <si>
-    <t>(079) 452-2199</t>
-  </si>
-  <si>
-    <t>phuong.lexuan@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Phạm Nguyên Đức</t>
-  </si>
-  <si>
-    <t>(077) 743-7069</t>
-  </si>
-  <si>
-    <t>duc.pham@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Huy</t>
-  </si>
-  <si>
-    <t>(078) 757-5997</t>
-  </si>
-  <si>
-    <t>huy.nguyenvan@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Trần Thị Nhàn</t>
-  </si>
-  <si>
-    <t>(096) 649-5870</t>
-  </si>
-  <si>
-    <t>nhan.tran@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Mai Đăng Tùng</t>
-  </si>
-  <si>
-    <t>(070) 405-8094</t>
-  </si>
-  <si>
-    <t>tung.mai@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Ngô Thị Trung Hiếu</t>
-  </si>
-  <si>
-    <t>(097) 811-3915</t>
-  </si>
-  <si>
-    <t>hieu.ngo@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Tôn Nữ Minh Trang</t>
-  </si>
-  <si>
-    <t>(093) 596-9600</t>
-  </si>
-  <si>
-    <t>trang.ton@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Huỳnh Ngọc Minh</t>
-  </si>
-  <si>
-    <t>(090) 593-7472</t>
-  </si>
-  <si>
-    <t>minh.huynh@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Phạm Văn Phú Thịnh</t>
-  </si>
-  <si>
-    <t>(090) 590-1869</t>
-  </si>
-  <si>
-    <t>thinh.pham@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Hồ Khắc Hoàng</t>
-  </si>
-  <si>
-    <t>(097) 345-1505</t>
-  </si>
-  <si>
-    <t>hoang.ho@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Trương Thị Vĩ Ngọc</t>
-  </si>
-  <si>
-    <t>(093) 494-4470</t>
-  </si>
-  <si>
-    <t>ngoc.truong@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>BA QA</t>
-  </si>
-  <si>
-    <t>Trần Trọng Tuyển</t>
-  </si>
-  <si>
-    <t>(094) 643-9269</t>
-  </si>
-  <si>
-    <t>tuyen.trantrong@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Hồ Kim Lân</t>
-  </si>
-  <si>
-    <t>(078) 247-6853</t>
-  </si>
-  <si>
-    <t>lan.ho@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Dương Quang Sang</t>
-  </si>
-  <si>
-    <t>(093) 535-3972</t>
-  </si>
-  <si>
-    <t>sang.duong@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Trần Thị Tuyết</t>
-  </si>
-  <si>
-    <t>(094) 422-6877</t>
-  </si>
-  <si>
-    <t>tuyet.tran@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Thành</t>
-  </si>
-  <si>
-    <t>(090) 657-1099</t>
-  </si>
-  <si>
-    <t>thanh.nguyencong@asnet.com.vn</t>
-  </si>
-  <si>
-    <t>BS</t>
-  </si>
-  <si>
-    <t>HPT</t>
-  </si>
-  <si>
-    <t>Trần Công Thành</t>
-  </si>
-  <si>
-    <t>(090) 886-4282</t>
-  </si>
-  <si>
-    <t>thanh.trancong@asnet.com.vn</t>
+    <t>DevOps</t>
   </si>
   <si>
     <t>Lê Ngọc Tân</t>
@@ -2537,7 +2543,8 @@
     <t>Lost Temple</t>
   </si>
   <si>
-    <t>CI/CD pipelines, deployment automation...</t>
+    <t>Game Development team is responsible for building and maintaining game products,
+including gameplay features, graphics systems, and performance optimization.</t>
   </si>
   <si>
     <t>Athena</t>
@@ -2579,15 +2586,11 @@
     <t>Big Game Hunter</t>
   </si>
   <si>
-    <t>- Develop and maintain backend and frontend applications
-- Fix software bugs and system errors
-- Implement new features based on business requirements
-- Build and maintain APIs
-- Manage and optimize databases
-- Improve system performance and scalability
-- Handle deployment and technical releases
-- Integrate third-party services
-- Maintain source code and technical documentation</t>
+    <t xml:space="preserve">Develop and maintain backend and frontend applications
+</t>
+  </si>
+  <si>
+    <t>CI/CD pipelines,manages CI pipelines, handles cloud systems, manages infrastructure, server deployment, deployment automation, DevOps, ...</t>
   </si>
 </sst>
 </file>
@@ -3091,9 +3094,11 @@
       <c r="D9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="F9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>32</v>
@@ -3104,20 +3109,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4">
         <v>31232.0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="F10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>32</v>
@@ -3128,25 +3135,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4">
         <v>29911.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>14</v>
@@ -3154,25 +3161,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="4">
         <v>30857.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>14</v>
@@ -3180,25 +3187,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4">
         <v>30690.0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>14</v>
@@ -3206,25 +3213,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="4">
         <v>33408.0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>14</v>
@@ -3232,25 +3239,25 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="4">
         <v>34113.0</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>14</v>
@@ -3258,25 +3265,25 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="4">
         <v>35313.0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>14</v>
@@ -3284,25 +3291,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="4">
         <v>34267.0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>14</v>
@@ -3310,25 +3317,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="4">
         <v>34724.0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>14</v>
@@ -3336,25 +3343,25 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="4">
         <v>34713.0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>14</v>
@@ -3362,23 +3369,23 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" s="4">
         <v>34819.0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>14</v>
@@ -3386,25 +3393,25 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B21" s="4">
         <v>36977.0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>14</v>
@@ -3412,23 +3419,23 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" s="4">
         <v>36619.0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>14</v>
@@ -3436,25 +3443,25 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="4">
         <v>36526.0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>14</v>
@@ -3462,23 +3469,23 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="4">
         <v>37256.0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>14</v>
@@ -3486,25 +3493,25 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="4">
         <v>29900.0</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>14</v>
@@ -3512,23 +3519,23 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="4">
         <v>32115.0</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>14</v>
@@ -3536,25 +3543,25 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="4">
         <v>33219.0</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>14</v>
@@ -3562,25 +3569,25 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="4">
         <v>34113.0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>14</v>
@@ -3588,25 +3595,25 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="4">
         <v>34266.0</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>14</v>
@@ -3614,25 +3621,25 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="4">
         <v>33979.0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>14</v>
@@ -3640,25 +3647,25 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="4">
         <v>34347.0</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>14</v>
@@ -3666,25 +3673,25 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="4">
         <v>32385.0</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>14</v>
@@ -3692,25 +3699,25 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="4">
         <v>34547.0</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>14</v>
@@ -3718,25 +3725,25 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" s="4">
         <v>35325.0</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>14</v>
@@ -3744,25 +3751,25 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" s="4">
         <v>35408.0</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>14</v>
@@ -3770,25 +3777,25 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" s="4">
         <v>35957.0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>14</v>
@@ -3796,25 +3803,25 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B37" s="4">
         <v>36513.0</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>14</v>
@@ -3822,25 +3829,25 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" s="4">
         <v>36451.0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>14</v>
@@ -3848,25 +3855,25 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B39" s="4">
         <v>36351.0</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>14</v>
@@ -3874,25 +3881,25 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" s="4">
         <v>34737.0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>14</v>
@@ -3900,25 +3907,25 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" s="4">
         <v>36485.0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>14</v>
@@ -3926,23 +3933,23 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B42" s="4">
         <v>30090.0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>14</v>
@@ -3950,25 +3957,25 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" s="4">
         <v>33536.0</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>14</v>
@@ -3976,25 +3983,25 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" s="4">
         <v>33727.0</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>14</v>
@@ -4002,25 +4009,25 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" s="4">
         <v>34863.0</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>14</v>
@@ -4028,25 +4035,25 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" s="4">
         <v>33256.0</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>14</v>
@@ -4054,23 +4061,23 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" s="4">
         <v>32964.0</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>14</v>
@@ -4078,25 +4085,25 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B48" s="4">
         <v>35361.0</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>14</v>
@@ -4104,25 +4111,25 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B49" s="4">
         <v>36460.0</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>14</v>
@@ -4130,25 +4137,25 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B50" s="4">
         <v>35100.0</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>14</v>
@@ -4156,25 +4163,25 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" s="4">
         <v>32935.0</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>14</v>
@@ -4182,25 +4189,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" s="4">
         <v>36192.0</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>14</v>
@@ -4208,25 +4215,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B53" s="4">
         <v>37188.0</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>14</v>
@@ -4234,25 +4241,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="4">
         <v>35070.0</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>14</v>
@@ -4260,25 +4267,25 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" s="4">
         <v>34330.0</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>14</v>
@@ -4286,25 +4293,23 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" s="4">
         <v>32827.0</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E56" s="1" t="s">
         <v>193</v>
       </c>
+      <c r="E56" s="1"/>
       <c r="F56" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>14</v>
@@ -4324,13 +4329,13 @@
         <v>197</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>14</v>
@@ -4350,13 +4355,13 @@
         <v>200</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>14</v>
@@ -4376,13 +4381,13 @@
         <v>203</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>14</v>
@@ -4402,13 +4407,13 @@
         <v>206</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>14</v>
@@ -4428,13 +4433,13 @@
         <v>209</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>14</v>
@@ -4454,13 +4459,13 @@
         <v>212</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>14</v>
@@ -4480,13 +4485,13 @@
         <v>215</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>14</v>
@@ -4500,19 +4505,19 @@
         <v>36469.0</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>217</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>14</v>
@@ -4532,13 +4537,13 @@
         <v>220</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>14</v>
@@ -4558,13 +4563,13 @@
         <v>223</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>14</v>
@@ -4584,13 +4589,13 @@
         <v>226</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>14</v>
@@ -4610,13 +4615,13 @@
         <v>229</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>14</v>
@@ -4636,13 +4641,13 @@
         <v>232</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>14</v>
@@ -4662,10 +4667,10 @@
         <v>235</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>236</v>
@@ -4688,10 +4693,10 @@
         <v>239</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>236</v>
@@ -4714,10 +4719,10 @@
         <v>242</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>243</v>
@@ -4740,10 +4745,10 @@
         <v>246</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>243</v>
@@ -4766,10 +4771,10 @@
         <v>249</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>243</v>
@@ -4792,10 +4797,10 @@
         <v>252</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>243</v>
@@ -4818,10 +4823,10 @@
         <v>255</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>243</v>
@@ -4844,10 +4849,10 @@
         <v>258</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>243</v>
@@ -4870,10 +4875,10 @@
         <v>261</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>243</v>
@@ -4896,10 +4901,10 @@
         <v>264</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>243</v>
@@ -4923,7 +4928,7 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>243</v>
@@ -4946,10 +4951,10 @@
         <v>270</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>243</v>
@@ -4972,10 +4977,10 @@
         <v>273</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>243</v>
@@ -4998,10 +5003,10 @@
         <v>276</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>243</v>
@@ -5027,7 +5032,7 @@
         <v>280</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>243</v>
@@ -5050,10 +5055,10 @@
         <v>283</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>243</v>
@@ -5076,10 +5081,10 @@
         <v>286</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>243</v>
@@ -5102,10 +5107,10 @@
         <v>289</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>243</v>
@@ -5131,7 +5136,7 @@
         <v>280</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>243</v>
@@ -5178,10 +5183,10 @@
         <v>300</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>193</v>
+        <v>301</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>47</v>
+        <v>302</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>297</v>
@@ -5192,16 +5197,16 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B91" s="4">
         <v>34851.0</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="2" t="s">
@@ -5216,16 +5221,16 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B92" s="4">
         <v>35204.0</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="2" t="s">
@@ -5240,22 +5245,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B93" s="4">
         <v>36343.0</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>297</v>
@@ -5266,22 +5271,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B94" s="4">
         <v>36794.0</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>297</v>
@@ -5292,25 +5297,25 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B95" s="4">
         <v>30505.0</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>14</v>
@@ -5318,23 +5323,23 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B96" s="4">
         <v>31477.0</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>14</v>
@@ -5342,25 +5347,25 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B97" s="4">
         <v>31770.0</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>14</v>
@@ -5368,23 +5373,23 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B98" s="4">
         <v>33056.0</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>14</v>
@@ -5392,23 +5397,23 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B99" s="4">
         <v>33202.0</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>14</v>
@@ -5416,25 +5421,25 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B100" s="4">
         <v>32047.0</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>14</v>
@@ -5442,25 +5447,25 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B101" s="4">
         <v>29627.0</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>14</v>
@@ -5468,25 +5473,25 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B102" s="4">
         <v>33003.0</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>14</v>
@@ -5494,23 +5499,23 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B103" s="4">
         <v>33010.0</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>14</v>
@@ -5518,23 +5523,23 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B104" s="4">
         <v>33096.0</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>14</v>
@@ -5542,23 +5547,23 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B105" s="4">
         <v>33017.0</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>14</v>
@@ -5566,25 +5571,25 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B106" s="4">
         <v>32062.0</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>14</v>
@@ -5592,25 +5597,25 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B107" s="4">
         <v>33731.0</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>14</v>
@@ -5618,25 +5623,25 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B108" s="4">
         <v>34323.0</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>14</v>
@@ -5644,25 +5649,25 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B109" s="4">
         <v>34919.0</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>14</v>
@@ -5670,25 +5675,25 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B110" s="4">
         <v>33646.0</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>14</v>
@@ -5696,25 +5701,25 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B111" s="4">
         <v>34813.0</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>14</v>
@@ -5722,25 +5727,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B112" s="4">
         <v>34120.0</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>14</v>
@@ -5748,25 +5753,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B113" s="4">
         <v>34693.0</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>14</v>
@@ -5774,25 +5779,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B114" s="4">
         <v>32958.0</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>14</v>
@@ -5800,25 +5805,25 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B115" s="4">
         <v>32660.0</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>14</v>
@@ -5826,25 +5831,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B116" s="4">
         <v>34486.0</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>14</v>
@@ -5852,25 +5857,25 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B117" s="4">
         <v>35339.0</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>14</v>
@@ -5878,23 +5883,23 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B118" s="4">
         <v>35229.0</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>14</v>
@@ -5902,25 +5907,25 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B119" s="4">
         <v>34376.0</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>14</v>
@@ -5928,25 +5933,25 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B120" s="4">
         <v>36638.0</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>14</v>
@@ -5954,25 +5959,25 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B121" s="4">
         <v>36947.0</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>14</v>
@@ -5980,25 +5985,25 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B122" s="4">
         <v>32293.0</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>14</v>
@@ -6006,23 +6011,23 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B123" s="4">
         <v>34148.0</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>14</v>
@@ -6030,25 +6035,25 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B124" s="4">
         <v>36288.0</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>14</v>
@@ -6056,25 +6061,25 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B125" s="4">
         <v>35662.0</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>14</v>
@@ -6082,23 +6087,23 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B126" s="4">
         <v>36379.0</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>14</v>
@@ -6106,25 +6111,25 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B127" s="4">
         <v>37136.0</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>14</v>
@@ -6132,25 +6137,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B128" s="4">
         <v>36802.0</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>14</v>
@@ -6158,25 +6163,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B129" s="4">
         <v>30587.0</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>14</v>
@@ -6184,23 +6189,23 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B130" s="4">
         <v>31210.0</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>14</v>
@@ -6208,25 +6213,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B131" s="4">
         <v>31038.0</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>14</v>
@@ -6234,25 +6239,25 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B132" s="4">
         <v>31512.0</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>14</v>
@@ -6260,25 +6265,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B133" s="4">
         <v>31413.0</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>14</v>
@@ -6286,23 +6291,23 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B134" s="4">
         <v>30946.0</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>14</v>
@@ -6310,25 +6315,25 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B135" s="4">
         <v>31938.0</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>14</v>
@@ -6336,25 +6341,25 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B136" s="4">
         <v>32567.0</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>14</v>
@@ -6362,25 +6367,25 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B137" s="4">
         <v>32610.0</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>14</v>
@@ -6388,25 +6393,25 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B138" s="4">
         <v>32695.0</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>14</v>
@@ -6414,25 +6419,25 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B139" s="4">
         <v>33723.0</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>14</v>
@@ -6440,25 +6445,25 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B140" s="4">
         <v>34344.0</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>14</v>
@@ -6466,25 +6471,25 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B141" s="4">
         <v>32968.0</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>14</v>
@@ -6492,25 +6497,25 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B142" s="4">
         <v>35389.0</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>14</v>
@@ -6518,25 +6523,25 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B143" s="4">
         <v>33920.0</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>14</v>
@@ -6544,25 +6549,25 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B144" s="4">
         <v>32583.0</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>14</v>
@@ -6570,25 +6575,25 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B145" s="4">
         <v>33552.0</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>14</v>
@@ -6596,25 +6601,25 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B146" s="4">
         <v>33626.0</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>14</v>
@@ -6622,25 +6627,25 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B147" s="4">
         <v>35065.0</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>14</v>
@@ -6648,25 +6653,25 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B148" s="4">
         <v>35009.0</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>14</v>
@@ -6674,25 +6679,25 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B149" s="4">
         <v>35723.0</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>14</v>
@@ -6700,25 +6705,25 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B150" s="4">
         <v>33881.0</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>14</v>
@@ -6726,25 +6731,25 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B151" s="4">
         <v>34984.0</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>14</v>
@@ -6752,25 +6757,25 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B152" s="4">
         <v>35772.0</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>14</v>
@@ -6778,25 +6783,25 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B153" s="4">
         <v>33301.0</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>14</v>
@@ -6804,25 +6809,25 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B154" s="4">
         <v>31168.0</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>14</v>
@@ -6830,25 +6835,25 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B155" s="4">
         <v>36170.0</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>14</v>
@@ -6856,25 +6861,25 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B156" s="4">
         <v>36158.0</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>14</v>
@@ -6882,25 +6887,25 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B157" s="4">
         <v>34783.0</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>14</v>
@@ -6908,25 +6913,25 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B158" s="4">
         <v>36316.0</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>14</v>
@@ -6934,25 +6939,25 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B159" s="4">
         <v>36078.0</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>14</v>
@@ -6960,25 +6965,25 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B160" s="4">
         <v>36703.0</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>14</v>
@@ -6986,25 +6991,25 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B161" s="4">
         <v>36148.0</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>14</v>
@@ -7012,25 +7017,25 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B162" s="4">
         <v>31887.0</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>14</v>
@@ -7038,25 +7043,25 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B163" s="4">
         <v>35457.0</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>14</v>
@@ -7064,25 +7069,25 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B164" s="4">
         <v>35590.0</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>14</v>
@@ -7090,25 +7095,25 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B165" s="4">
         <v>36125.0</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>14</v>
@@ -7116,25 +7121,25 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B166" s="4">
         <v>33918.0</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>14</v>
@@ -7142,25 +7147,25 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B167" s="4">
         <v>37527.0</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>14</v>
@@ -7168,25 +7173,25 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B168" s="4">
         <v>33229.0</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>14</v>
@@ -7194,25 +7199,25 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B169" s="4">
         <v>33192.0</v>
       </c>
       <c r="C169" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G169" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>14</v>
@@ -7220,7 +7225,7 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B170" s="4">
         <v>33005.0</v>
@@ -7229,16 +7234,16 @@
         <v>9.733701248E9</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>14</v>
@@ -7246,25 +7251,25 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B171" s="4">
         <v>33271.0</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>14</v>
@@ -7272,25 +7277,25 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B172" s="4">
         <v>32875.0</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H172" s="1" t="s">
         <v>14</v>
@@ -7298,25 +7303,25 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B173" s="4">
         <v>33948.0</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H173" s="1" t="s">
         <v>14</v>
@@ -7324,25 +7329,25 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B174" s="4">
         <v>34429.0</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>14</v>
@@ -7350,25 +7355,25 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B175" s="4">
         <v>34280.0</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>14</v>
@@ -7376,25 +7381,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B176" s="4">
         <v>35297.0</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>14</v>
@@ -7402,25 +7407,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B177" s="4">
         <v>33770.0</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H177" s="1" t="s">
         <v>14</v>
@@ -7428,25 +7433,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B178" s="4">
         <v>32935.0</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>14</v>
@@ -7454,25 +7459,25 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B179" s="4">
         <v>33888.0</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>14</v>
@@ -7480,25 +7485,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B180" s="4">
         <v>32798.0</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>14</v>
@@ -7506,25 +7511,25 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B181" s="4">
         <v>35952.0</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>14</v>
@@ -7532,25 +7537,25 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B182" s="4">
         <v>36248.0</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>14</v>
@@ -7558,25 +7563,25 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B183" s="4">
         <v>36157.0</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>14</v>
@@ -7584,25 +7589,25 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B184" s="4">
         <v>36161.0</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>14</v>
@@ -7610,25 +7615,25 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B185" s="4">
         <v>36472.0</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H185" s="1" t="s">
         <v>14</v>
@@ -7636,25 +7641,25 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B186" s="4">
         <v>33837.0</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>14</v>
@@ -7662,25 +7667,25 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B187" s="4">
         <v>36450.0</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>14</v>
@@ -7688,25 +7693,25 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B188" s="4">
         <v>36482.0</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H188" s="1" t="s">
         <v>14</v>
@@ -7714,23 +7719,23 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B189" s="4">
         <v>35506.0</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E189" s="3"/>
       <c r="F189" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>14</v>
@@ -7738,25 +7743,25 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B190" s="4">
         <v>35691.0</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>14</v>
@@ -7764,25 +7769,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B191" s="4">
         <v>37132.0</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>14</v>
@@ -7790,25 +7795,25 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B192" s="4">
         <v>36461.0</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>14</v>
@@ -7816,25 +7821,25 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B193" s="4">
         <v>37347.0</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H193" s="1" t="s">
         <v>14</v>
@@ -7842,7 +7847,7 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B194" s="4">
         <v>37188.0</v>
@@ -7851,16 +7856,16 @@
         <v>214</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>14</v>
@@ -7868,25 +7873,25 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B195" s="4">
         <v>34614.0</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H195" s="1" t="s">
         <v>14</v>
@@ -7894,25 +7899,25 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B196" s="4">
         <v>36552.0</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>14</v>
@@ -7920,25 +7925,25 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B197" s="4">
         <v>36262.0</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H197" s="1" t="s">
         <v>14</v>
@@ -7946,25 +7951,25 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B198" s="4">
         <v>34044.0</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>14</v>
@@ -7972,25 +7977,25 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B199" s="4">
         <v>36744.0</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H199" s="1" t="s">
         <v>14</v>
@@ -7998,25 +8003,25 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B200" s="4">
         <v>33435.0</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H200" s="1" t="s">
         <v>14</v>
@@ -8024,23 +8029,23 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B201" s="4">
         <v>20207.0</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E201" s="3"/>
       <c r="F201" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H201" s="1" t="s">
         <v>14</v>
@@ -8048,23 +8053,23 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B202" s="4">
         <v>29354.0</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E202" s="3"/>
       <c r="F202" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H202" s="1" t="s">
         <v>14</v>
@@ -8072,25 +8077,25 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B203" s="4">
         <v>30649.0</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>14</v>
@@ -8098,23 +8103,23 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B204" s="4">
         <v>29707.0</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E204" s="3"/>
       <c r="F204" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>14</v>
@@ -8122,23 +8127,23 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B205" s="4">
         <v>31751.0</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E205" s="3"/>
       <c r="F205" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H205" s="1" t="s">
         <v>14</v>
@@ -8146,23 +8151,23 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B206" s="4">
         <v>28126.0</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E206" s="3"/>
       <c r="F206" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H206" s="1" t="s">
         <v>14</v>
@@ -8170,23 +8175,23 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B207" s="4">
         <v>27873.0</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E207" s="3"/>
       <c r="F207" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H207" s="1" t="s">
         <v>14</v>
@@ -8194,25 +8199,25 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B208" s="4">
         <v>31664.0</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H208" s="1" t="s">
         <v>14</v>
@@ -8220,23 +8225,23 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B209" s="4">
         <v>30356.0</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E209" s="3"/>
       <c r="F209" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H209" s="1" t="s">
         <v>14</v>
@@ -8244,25 +8249,25 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B210" s="4">
         <v>32046.0</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>14</v>
@@ -8270,25 +8275,25 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B211" s="4">
         <v>32736.0</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>14</v>
@@ -8296,23 +8301,23 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B212" s="4">
         <v>31011.0</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E212" s="3"/>
       <c r="F212" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H212" s="1" t="s">
         <v>14</v>
@@ -8320,23 +8325,23 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B213" s="4">
         <v>32840.0</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E213" s="3"/>
       <c r="F213" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H213" s="1" t="s">
         <v>14</v>
@@ -8344,23 +8349,23 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B214" s="4">
         <v>32843.0</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E214" s="3"/>
       <c r="F214" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>14</v>
@@ -8368,23 +8373,23 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B215" s="4">
         <v>29457.0</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E215" s="3"/>
       <c r="F215" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H215" s="1" t="s">
         <v>14</v>
@@ -8392,25 +8397,25 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B216" s="4">
         <v>30023.0</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H216" s="1" t="s">
         <v>14</v>
@@ -8418,25 +8423,25 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B217" s="4">
         <v>33128.0</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>14</v>
@@ -8444,25 +8449,25 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B218" s="4">
         <v>30162.0</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H218" s="1" t="s">
         <v>14</v>
@@ -8470,25 +8475,25 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B219" s="4">
         <v>30613.0</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H219" s="1" t="s">
         <v>14</v>
@@ -8496,25 +8501,25 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B220" s="4">
         <v>31348.0</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>14</v>
@@ -8522,25 +8527,25 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B221" s="4">
         <v>33201.0</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>14</v>
@@ -8548,25 +8553,25 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B222" s="4">
         <v>32632.0</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H222" s="1" t="s">
         <v>14</v>
@@ -8574,25 +8579,25 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B223" s="4">
         <v>31941.0</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>14</v>
@@ -8600,25 +8605,25 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B224" s="4">
         <v>33696.0</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>14</v>
@@ -8626,25 +8631,25 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B225" s="4">
         <v>33914.0</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>14</v>
@@ -8652,25 +8657,25 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B226" s="4">
         <v>34398.0</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>14</v>
@@ -8678,25 +8683,25 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B227" s="4">
         <v>32693.0</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H227" s="1" t="s">
         <v>14</v>
@@ -8704,23 +8709,23 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B228" s="4">
         <v>32874.0</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E228" s="3"/>
       <c r="F228" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>14</v>
@@ -8728,23 +8733,23 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B229" s="4">
         <v>32489.0</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E229" s="3"/>
       <c r="F229" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>14</v>
@@ -8752,23 +8757,23 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B230" s="4">
         <v>32274.0</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H230" s="1" t="s">
         <v>14</v>
@@ -8776,23 +8781,23 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B231" s="4">
         <v>34313.0</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E231" s="3"/>
       <c r="F231" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>14</v>
@@ -8800,13 +8805,13 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B232" s="4">
         <v>32371.0</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D232" s="5"/>
       <c r="E232" s="3"/>
@@ -8814,7 +8819,7 @@
         <v>18</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H232" s="1" t="s">
         <v>14</v>
@@ -8822,23 +8827,23 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B233" s="4">
         <v>33320.0</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E233" s="3"/>
       <c r="F233" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H233" s="1" t="s">
         <v>14</v>
@@ -8846,23 +8851,23 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B234" s="4">
         <v>32336.0</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E234" s="3"/>
       <c r="F234" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>14</v>
@@ -8870,25 +8875,25 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B235" s="4">
         <v>33711.0</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>14</v>
@@ -8896,25 +8901,25 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B236" s="4">
         <v>34814.0</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H236" s="1" t="s">
         <v>14</v>
@@ -8922,25 +8927,25 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B237" s="4">
         <v>34250.0</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H237" s="1" t="s">
         <v>14</v>
@@ -8948,25 +8953,25 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B238" s="4">
         <v>35206.0</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>14</v>
@@ -8974,25 +8979,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B239" s="4">
         <v>34700.0</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H239" s="1" t="s">
         <v>14</v>
@@ -9000,25 +9005,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B240" s="4">
         <v>35354.0</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>14</v>
@@ -9026,25 +9031,25 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B241" s="4">
         <v>33490.0</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H241" s="1" t="s">
         <v>14</v>
@@ -9052,23 +9057,23 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B242" s="4">
         <v>34759.0</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E242" s="3"/>
       <c r="F242" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H242" s="1" t="s">
         <v>14</v>
@@ -9076,23 +9081,23 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B243" s="4">
         <v>32901.0</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E243" s="3"/>
       <c r="F243" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H243" s="1" t="s">
         <v>14</v>
@@ -9100,25 +9105,25 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B244" s="4">
         <v>34884.0</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>14</v>
@@ -9126,25 +9131,25 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B245" s="4">
         <v>35303.0</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H245" s="1" t="s">
         <v>14</v>
@@ -9152,23 +9157,23 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B246" s="4">
         <v>35481.0</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E246" s="3"/>
       <c r="F246" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>14</v>
@@ -9176,23 +9181,23 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B247" s="4">
         <v>33696.0</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E247" s="3"/>
       <c r="F247" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>14</v>
@@ -9200,23 +9205,23 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B248" s="4">
         <v>36810.0</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E248" s="3"/>
       <c r="F248" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>14</v>
@@ -9224,25 +9229,25 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B249" s="4">
         <v>33439.0</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H249" s="1" t="s">
         <v>14</v>
@@ -9250,25 +9255,25 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B250" s="4">
         <v>33734.0</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H250" s="1" t="s">
         <v>14</v>
@@ -9276,23 +9281,23 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B251" s="4">
         <v>32056.0</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E251" s="3"/>
       <c r="F251" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>14</v>
@@ -9300,25 +9305,25 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B252" s="4">
         <v>33477.0</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H252" s="1" t="s">
         <v>14</v>
@@ -9326,25 +9331,25 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B253" s="4">
         <v>35932.0</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H253" s="1" t="s">
         <v>14</v>
@@ -9352,23 +9357,23 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B254" s="4">
         <v>32498.0</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E254" s="3"/>
       <c r="F254" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H254" s="1" t="s">
         <v>14</v>
@@ -9376,23 +9381,23 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B255" s="4">
         <v>32929.0</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E255" s="3"/>
       <c r="F255" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>14</v>
@@ -9400,25 +9405,25 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B256" s="4">
         <v>36382.0</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H256" s="1" t="s">
         <v>14</v>
@@ -9426,23 +9431,23 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B257" s="4">
         <v>22130.0</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D257" s="5"/>
       <c r="E257" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H257" s="1" t="s">
         <v>14</v>
@@ -9450,23 +9455,23 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B258" s="4">
         <v>25813.0</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D258" s="5"/>
       <c r="E258" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H258" s="1" t="s">
         <v>14</v>
@@ -9474,23 +9479,23 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B259" s="4">
         <v>27431.0</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D259" s="5"/>
       <c r="E259" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H259" s="1" t="s">
         <v>14</v>
@@ -9498,23 +9503,23 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B260" s="4">
         <v>26037.0</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D260" s="5"/>
       <c r="E260" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H260" s="1" t="s">
         <v>14</v>
@@ -9522,23 +9527,23 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B261" s="4">
         <v>31090.0</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D261" s="5"/>
       <c r="E261" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H261" s="1" t="s">
         <v>14</v>
@@ -9546,23 +9551,23 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B262" s="4">
         <v>30841.0</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D262" s="5"/>
       <c r="E262" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H262" s="1" t="s">
         <v>14</v>
@@ -9570,23 +9575,23 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B263" s="4">
         <v>32216.0</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D263" s="5"/>
       <c r="E263" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H263" s="1" t="s">
         <v>14</v>
@@ -9594,23 +9599,23 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B264" s="4">
         <v>32444.0</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D264" s="5"/>
       <c r="E264" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H264" s="1" t="s">
         <v>14</v>
@@ -9618,23 +9623,23 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B265" s="4">
         <v>34659.0</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D265" s="5"/>
       <c r="E265" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H265" s="1" t="s">
         <v>14</v>
@@ -9642,23 +9647,23 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B266" s="4">
         <v>30883.0</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D266" s="5"/>
       <c r="E266" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H266" s="1" t="s">
         <v>14</v>
@@ -9666,23 +9671,23 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B267" s="4">
         <v>25477.0</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D267" s="5"/>
       <c r="E267" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H267" s="1" t="s">
         <v>14</v>
@@ -9690,23 +9695,23 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B268" s="4">
         <v>24070.0</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D268" s="5"/>
       <c r="E268" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H268" s="1" t="s">
         <v>14</v>
@@ -9714,23 +9719,23 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B269" s="4">
         <v>33223.0</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D269" s="5"/>
       <c r="E269" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H269" s="1" t="s">
         <v>14</v>
@@ -9738,23 +9743,23 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B270" s="4">
         <v>25614.0</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D270" s="5"/>
       <c r="E270" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>14</v>
@@ -9762,23 +9767,23 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B271" s="4">
         <v>24416.0</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D271" s="5"/>
       <c r="E271" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>14</v>
@@ -9786,23 +9791,23 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B272" s="4">
         <v>30592.0</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D272" s="5"/>
       <c r="E272" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H272" s="1" t="s">
         <v>14</v>
@@ -15658,13 +15663,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="2">
@@ -15672,21 +15677,21 @@
         <v>194</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4">
@@ -15694,21 +15699,21 @@
         <v>296</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6">
@@ -15716,21 +15721,21 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8">
@@ -15738,21 +15743,32 @@
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>857</v>
       </c>
     </row>
   </sheetData>
